--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -426,15 +426,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,25 +444,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Test Case Description</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Test Case Description</t>
+          <t>Precondition</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Precondition</t>
+          <t>Input/Test Steps</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Input/Test Steps</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Base URL &amp; API</t>
         </is>
@@ -477,27 +471,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] Point lookup: query a Person by primary id returns exactly one vertex.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Point lookup: query a Person by primary id returns exactly one vertex.</t>
+          <t>HA cluster active; sample graph loaded.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; sample graph loaded.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>1. Open gsql on graph social
 2. Run point-lookup query for id p1
 3. Verify one vertex returned</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>gsql -g social 'INTERPRET QUERY(){ ... WHERE v.id=="p1" }'</t>
         </is>
@@ -511,27 +500,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] 1-hop traversal: friends of a Person are returned.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1-hop traversal: friends of a Person are returned.</t>
+          <t>HA cluster active; sample graph loaded.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; sample graph loaded.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>1. Open gsql on graph social
 2. Run 1-hop Friendship traversal from p1
 3. Verify neighbour set</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>gsql -g social 'INTERPRET QUERY(){ ... -(Friendship)- Person }'</t>
         </is>
@@ -545,27 +529,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] Aggregation: count of all Person vertices equals 5000.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Aggregation: count of all Person vertices equals 5000.</t>
+          <t>HA cluster active; sample graph loaded.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; sample graph loaded.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1. Open gsql on graph social
 2. Run SumAccum count over all Person
 3. Verify count == 5000</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>gsql -g social 'INTERPRET QUERY(){ ACCUM @@n+=1 }'</t>
         </is>
@@ -579,27 +558,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] Multi-hop traversal: 2-hop friendship expansion returns a result set.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Multi-hop traversal: 2-hop friendship expansion returns a result set.</t>
+          <t>HA cluster active; sample graph loaded.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; sample graph loaded.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>1. Open gsql on graph social
 2. Run 2-hop traversal from p1
 3. Verify non-empty result</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>gsql -g social 'INTERPRET QUERY(){ 2-hop }'</t>
         </is>
@@ -613,27 +587,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] Service health: all critical services (GPE, GSE, RESTPP, GSQL) are Online.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Service health: all critical services (GPE, GSE, RESTPP, GSQL) are Online.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>1. Run gadmin status -v
 2. Parse service states
 3. Verify all critical services Online</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>gadmin status -v</t>
         </is>
@@ -647,27 +616,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>[Positive] Loading job: load Person rows from a CSV file source; vertex count increases.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Loading job: load Person rows from a CSV file source; vertex count increases.</t>
+          <t>HA cluster active; loading job defined.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; loading job defined.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1. Generate CSV of 200 rows
 2. RUN LOADING JOB load_social with the CSV
 3. Verify LOAD SUCCESSFUL and count += 200</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>gsql -g social 'RUN LOADING JOB load_social USING f_person="...csv"'</t>
         </is>
@@ -681,20 +645,15 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Data-node hard crash: kill a node; measure availability and MTTR.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Data-node hard crash: kill a node; measure availability and MTTR.</t>
+          <t>HA cluster active; probe running.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe running.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>1. Start availability probe
 2. docker kill tg2
@@ -702,7 +661,7 @@
 4. Recover and measure MTTR</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>docker kill tg2 ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -716,20 +675,15 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Graceful node shutdown: stop a node; measure recovery.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Graceful node shutdown: stop a node; measure recovery.</t>
+          <t>HA cluster active; probe running.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe running.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>1. Start probe
 2. docker stop tg2
@@ -737,7 +691,7 @@
 4. Recover</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>docker stop tg2 ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -751,20 +705,15 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Frozen node: pause a node (up but unresponsive); measure recovery.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Frozen node: pause a node (up but unresponsive); measure recovery.</t>
+          <t>HA cluster active; probe running.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe running.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1. Start probe
 2. docker pause tg3
@@ -772,7 +721,7 @@
 4. Unpause</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>docker pause tg3 ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -786,20 +735,15 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Network partition: isolate a node; measure rejoin behaviour.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Network partition: isolate a node; measure rejoin behaviour.</t>
+          <t>HA cluster active; probe running.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe running.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>1. Start probe
 2. Disconnect tg3 from network
@@ -807,7 +751,7 @@
 4. Reconnect</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>docker network disconnect tgnet tg3 ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -821,20 +765,15 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Single-component failure: stop GPE on one node; measure behaviour.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Single-component failure: stop GPE on one node; measure behaviour.</t>
+          <t>HA cluster active; probe running.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe running.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>1. Start probe
 2. gadmin stop GPE_1#2
@@ -842,7 +781,7 @@
 4. Restart services</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>gadmin stop GPE ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -856,20 +795,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Master/gateway-node crash: kill tg1; observe from a surviving node.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Master/gateway-node crash: kill tg1; observe from a surviving node.</t>
+          <t>HA cluster active; probe on tg2.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active; probe on tg2.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. Start probe on tg2 gateway
 2. docker kill tg1
@@ -877,7 +811,7 @@
 4. Recover</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>docker kill tg1 ; http://localhost:14241/...</t>
         </is>
@@ -891,20 +825,15 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Service crash on node loss: killing a node takes its GPE/GSE/RESTPP instances down; a replica stays Online.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Service crash on node loss: killing a node takes its GPE/GSE/RESTPP instances down; a replica stays Online.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. Record baseline gadmin status
 2. docker kill tg2
@@ -912,7 +841,7 @@
 4. Verify tg2 services down and a GPE replica Online</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>docker kill tg2 ; gadmin status -v</t>
         </is>
@@ -926,20 +855,15 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Write durability under crash: writes during a node crash are not lost.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Write durability under crash: writes during a node crash are not lost.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. Record count
 2. docker kill tg3
@@ -947,7 +871,7 @@
 4. Recover; verify no acknowledged write lost</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>docker kill tg3 ; POST http://localhost:14240/restpp/graph/social</t>
         </is>
@@ -961,20 +885,15 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Failure</t>
+          <t>[Failure] Write durability under partition: ambiguous writes; nothing acknowledged is lost.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Write durability under partition: ambiguous writes; nothing acknowledged is lost.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. Record count
 2. Partition tg2
@@ -982,7 +901,7 @@
 4. Heal; verify durability</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>network disconnect tg2 ; POST http://localhost:14240/restpp/graph/social</t>
         </is>
@@ -996,27 +915,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>[Negative] Invalid query is rejected gracefully and does not crash the cluster.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Invalid query is rejected gracefully and does not crash the cluster.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. Run an invalid GSQL query
 2. Verify an error is returned
 3. Verify the gateway still serves</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>gsql -g social '&lt;invalid&gt;' ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>
@@ -1030,20 +944,15 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Boundary</t>
+          <t>[Boundary] Two-node failure exceeds RF=2 tolerance; cluster must recover after nodes return.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Two-node failure exceeds RF=2 tolerance; cluster must recover after nodes return.</t>
+          <t>HA cluster active.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>HA cluster active.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. docker kill tg2 and tg3
 2. Observe availability (likely lost)
@@ -1051,7 +960,7 @@
 4. Verify cluster recovers</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>docker kill tg2 tg3 ; GET http://localhost:14240/restpp/query/social/ping_count</t>
         </is>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -966,6 +966,38 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TC-CFG-001</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>[Positive] Configuration change: set a service config variable, apply and restart all; the value takes effect and all services return Online.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>HA cluster active.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1. gadmin config get RESTPP.Factory.DefaultQueryTimeoutSec (baseline)
+2. gadmin config set &lt;var&gt; &lt;new value&gt;
+3. gadmin config apply -y
+4. gadmin restart all -y
+5. gadmin status -v: verify all Online and the new value applied
+6. Revert the variable</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>gadmin config set RESTPP.Factory.DefaultQueryTimeoutSec 45 ; gadmin config apply -y ; gadmin restart all -y ; gadmin status -v</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
